--- a/review-results/河北实时运行及市场出清数据-20260925.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260925.xlsx
@@ -4284,8 +4284,12 @@
       <ns0:c r="C2" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D2" s="1"/>
-      <ns0:c r="E2" s="1"/>
+      <ns0:c r="D2" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="1" t="n">
+        <ns0:v>426.57</ns0:v>
+      </ns0:c>
       <ns0:c r="F2" s="1" t="n">
         <ns0:v>30</ns0:v>
       </ns0:c>
@@ -4330,8 +4334,12 @@
       <ns0:c r="C3" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D3" s="1"/>
-      <ns0:c r="E3" s="1"/>
+      <ns0:c r="D3" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="1" t="n">
+        <ns0:v>427.17</ns0:v>
+      </ns0:c>
       <ns0:c r="F3" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4376,8 +4384,12 @@
       <ns0:c r="C4" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D4" s="1"/>
-      <ns0:c r="E4" s="1"/>
+      <ns0:c r="D4" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" s="1" t="n">
+        <ns0:v>426.32</ns0:v>
+      </ns0:c>
       <ns0:c r="F4" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4422,8 +4434,12 @@
       <ns0:c r="C5" s="1" t="n">
         <ns0:v>1</ns0:v>
       </ns0:c>
-      <ns0:c r="D5" s="1"/>
-      <ns0:c r="E5" s="1"/>
+      <ns0:c r="D5" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="1" t="n">
+        <ns0:v>423.1</ns0:v>
+      </ns0:c>
       <ns0:c r="F5" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4468,8 +4484,12 @@
       <ns0:c r="C6" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D6" s="1"/>
-      <ns0:c r="E6" s="1"/>
+      <ns0:c r="D6" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="1" t="n">
+        <ns0:v>412.04</ns0:v>
+      </ns0:c>
       <ns0:c r="F6" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4514,8 +4534,12 @@
       <ns0:c r="C7" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D7" s="1"/>
-      <ns0:c r="E7" s="1"/>
+      <ns0:c r="D7" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="1" t="n">
+        <ns0:v>416.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F7" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4560,8 +4584,12 @@
       <ns0:c r="C8" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D8" s="1"/>
-      <ns0:c r="E8" s="1"/>
+      <ns0:c r="D8" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="1" t="n">
+        <ns0:v>412</ns0:v>
+      </ns0:c>
       <ns0:c r="F8" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4606,8 +4634,12 @@
       <ns0:c r="C9" s="1" t="n">
         <ns0:v>2</ns0:v>
       </ns0:c>
-      <ns0:c r="D9" s="1"/>
-      <ns0:c r="E9" s="1"/>
+      <ns0:c r="D9" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="1" t="n">
+        <ns0:v>410.29</ns0:v>
+      </ns0:c>
       <ns0:c r="F9" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4652,8 +4684,12 @@
       <ns0:c r="C10" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D10" s="1"/>
-      <ns0:c r="E10" s="1"/>
+      <ns0:c r="D10" s="1" t="n">
+        <ns0:v>457.66</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="1" t="n">
+        <ns0:v>456.52</ns0:v>
+      </ns0:c>
       <ns0:c r="F10" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4698,8 +4734,12 @@
       <ns0:c r="C11" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D11" s="1"/>
-      <ns0:c r="E11" s="1"/>
+      <ns0:c r="D11" s="1" t="n">
+        <ns0:v>457.66</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11" s="1" t="n">
+        <ns0:v>426.57</ns0:v>
+      </ns0:c>
       <ns0:c r="F11" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4744,8 +4784,12 @@
       <ns0:c r="C12" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D12" s="1"/>
-      <ns0:c r="E12" s="1"/>
+      <ns0:c r="D12" s="1" t="n">
+        <ns0:v>457.66</ns0:v>
+      </ns0:c>
+      <ns0:c r="E12" s="1" t="n">
+        <ns0:v>418.75</ns0:v>
+      </ns0:c>
       <ns0:c r="F12" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -4790,8 +4834,12 @@
       <ns0:c r="C13" s="1" t="n">
         <ns0:v>3</ns0:v>
       </ns0:c>
-      <ns0:c r="D13" s="1"/>
-      <ns0:c r="E13" s="1"/>
+      <ns0:c r="D13" s="1" t="n">
+        <ns0:v>457.66</ns0:v>
+      </ns0:c>
+      <ns0:c r="E13" s="1" t="n">
+        <ns0:v>426.35</ns0:v>
+      </ns0:c>
       <ns0:c r="F13" s="1" t="n">
         <ns0:v>30</ns0:v>
       </ns0:c>
@@ -4836,8 +4884,12 @@
       <ns0:c r="C14" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D14" s="1"/>
-      <ns0:c r="E14" s="1"/>
+      <ns0:c r="D14" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E14" s="1" t="n">
+        <ns0:v>428.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F14" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4882,8 +4934,12 @@
       <ns0:c r="C15" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D15" s="1"/>
-      <ns0:c r="E15" s="1"/>
+      <ns0:c r="D15" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E15" s="1" t="n">
+        <ns0:v>426.51</ns0:v>
+      </ns0:c>
       <ns0:c r="F15" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4928,8 +4984,12 @@
       <ns0:c r="C16" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D16" s="1"/>
-      <ns0:c r="E16" s="1"/>
+      <ns0:c r="D16" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E16" s="1" t="n">
+        <ns0:v>432.67</ns0:v>
+      </ns0:c>
       <ns0:c r="F16" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -4974,8 +5034,12 @@
       <ns0:c r="C17" s="1" t="n">
         <ns0:v>4</ns0:v>
       </ns0:c>
-      <ns0:c r="D17" s="1"/>
-      <ns0:c r="E17" s="1"/>
+      <ns0:c r="D17" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E17" s="1" t="n">
+        <ns0:v>430.14</ns0:v>
+      </ns0:c>
       <ns0:c r="F17" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5020,8 +5084,12 @@
       <ns0:c r="C18" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D18" s="1"/>
-      <ns0:c r="E18" s="1"/>
+      <ns0:c r="D18" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E18" s="1" t="n">
+        <ns0:v>427.26</ns0:v>
+      </ns0:c>
       <ns0:c r="F18" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5066,8 +5134,12 @@
       <ns0:c r="C19" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D19" s="1"/>
-      <ns0:c r="E19" s="1"/>
+      <ns0:c r="D19" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E19" s="1" t="n">
+        <ns0:v>425.48</ns0:v>
+      </ns0:c>
       <ns0:c r="F19" s="1" t="n">
         <ns0:v>40</ns0:v>
       </ns0:c>
@@ -5112,8 +5184,12 @@
       <ns0:c r="C20" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D20" s="1"/>
-      <ns0:c r="E20" s="1"/>
+      <ns0:c r="D20" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E20" s="1" t="n">
+        <ns0:v>418.75</ns0:v>
+      </ns0:c>
       <ns0:c r="F20" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -5158,8 +5234,12 @@
       <ns0:c r="C21" s="1" t="n">
         <ns0:v>5</ns0:v>
       </ns0:c>
-      <ns0:c r="D21" s="1"/>
-      <ns0:c r="E21" s="1"/>
+      <ns0:c r="D21" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E21" s="1" t="n">
+        <ns0:v>425.44</ns0:v>
+      </ns0:c>
       <ns0:c r="F21" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -5204,8 +5284,12 @@
       <ns0:c r="C22" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D22" s="1"/>
-      <ns0:c r="E22" s="1"/>
+      <ns0:c r="D22" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E22" s="1" t="n">
+        <ns0:v>411.82</ns0:v>
+      </ns0:c>
       <ns0:c r="F22" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -5250,8 +5334,12 @@
       <ns0:c r="C23" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D23" s="1"/>
-      <ns0:c r="E23" s="1"/>
+      <ns0:c r="D23" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E23" s="1" t="n">
+        <ns0:v>425.48</ns0:v>
+      </ns0:c>
       <ns0:c r="F23" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -5296,8 +5384,12 @@
       <ns0:c r="C24" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D24" s="1"/>
-      <ns0:c r="E24" s="1"/>
+      <ns0:c r="D24" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E24" s="1" t="n">
+        <ns0:v>405.35</ns0:v>
+      </ns0:c>
       <ns0:c r="F24" s="1" t="n">
         <ns0:v>40</ns0:v>
       </ns0:c>
@@ -5342,8 +5434,12 @@
       <ns0:c r="C25" s="1" t="n">
         <ns0:v>6</ns0:v>
       </ns0:c>
-      <ns0:c r="D25" s="1"/>
-      <ns0:c r="E25" s="1"/>
+      <ns0:c r="D25" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E25" s="1" t="n">
+        <ns0:v>411.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F25" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5388,8 +5484,12 @@
       <ns0:c r="C26" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D26" s="1"/>
-      <ns0:c r="E26" s="1"/>
+      <ns0:c r="D26" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E26" s="1" t="n">
+        <ns0:v>410.23</ns0:v>
+      </ns0:c>
       <ns0:c r="F26" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5434,8 +5534,12 @@
       <ns0:c r="C27" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D27" s="1"/>
-      <ns0:c r="E27" s="1"/>
+      <ns0:c r="D27" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E27" s="1" t="n">
+        <ns0:v>456.23</ns0:v>
+      </ns0:c>
       <ns0:c r="F27" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5480,8 +5584,12 @@
       <ns0:c r="C28" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D28" s="1"/>
-      <ns0:c r="E28" s="1"/>
+      <ns0:c r="D28" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E28" s="1" t="n">
+        <ns0:v>442.92</ns0:v>
+      </ns0:c>
       <ns0:c r="F28" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5526,8 +5634,12 @@
       <ns0:c r="C29" s="1" t="n">
         <ns0:v>7</ns0:v>
       </ns0:c>
-      <ns0:c r="D29" s="1"/>
-      <ns0:c r="E29" s="1"/>
+      <ns0:c r="D29" s="1" t="n">
+        <ns0:v>408.92</ns0:v>
+      </ns0:c>
+      <ns0:c r="E29" s="1" t="n">
+        <ns0:v>441.77</ns0:v>
+      </ns0:c>
       <ns0:c r="F29" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5572,8 +5684,12 @@
       <ns0:c r="C30" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D30" s="1"/>
-      <ns0:c r="E30" s="1"/>
+      <ns0:c r="D30" s="1" t="n">
+        <ns0:v>395.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E30" s="1" t="n">
+        <ns0:v>456.23</ns0:v>
+      </ns0:c>
       <ns0:c r="F30" s="1" t="n">
         <ns0:v>30</ns0:v>
       </ns0:c>
@@ -5618,8 +5734,12 @@
       <ns0:c r="C31" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D31" s="1"/>
-      <ns0:c r="E31" s="1"/>
+      <ns0:c r="D31" s="1" t="n">
+        <ns0:v>395.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E31" s="1" t="n">
+        <ns0:v>392.79</ns0:v>
+      </ns0:c>
       <ns0:c r="F31" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -5664,8 +5784,12 @@
       <ns0:c r="C32" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D32" s="1"/>
-      <ns0:c r="E32" s="1"/>
+      <ns0:c r="D32" s="1" t="n">
+        <ns0:v>395.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E32" s="1" t="n">
+        <ns0:v>383.41</ns0:v>
+      </ns0:c>
       <ns0:c r="F32" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -5710,8 +5834,12 @@
       <ns0:c r="C33" s="1" t="n">
         <ns0:v>8</ns0:v>
       </ns0:c>
-      <ns0:c r="D33" s="1"/>
-      <ns0:c r="E33" s="1"/>
+      <ns0:c r="D33" s="1" t="n">
+        <ns0:v>395.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E33" s="1" t="n">
+        <ns0:v>387.66</ns0:v>
+      </ns0:c>
       <ns0:c r="F33" s="1" t="n">
         <ns0:v>30</ns0:v>
       </ns0:c>
@@ -5756,8 +5884,12 @@
       <ns0:c r="C34" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D34" s="1"/>
-      <ns0:c r="E34" s="1"/>
+      <ns0:c r="D34" s="1" t="n">
+        <ns0:v>357.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E34" s="1" t="n">
+        <ns0:v>362.88</ns0:v>
+      </ns0:c>
       <ns0:c r="F34" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5802,8 +5934,12 @@
       <ns0:c r="C35" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D35" s="1"/>
-      <ns0:c r="E35" s="1"/>
+      <ns0:c r="D35" s="1" t="n">
+        <ns0:v>357.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E35" s="1" t="n">
+        <ns0:v>357.61</ns0:v>
+      </ns0:c>
       <ns0:c r="F35" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5848,8 +5984,12 @@
       <ns0:c r="C36" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D36" s="1"/>
-      <ns0:c r="E36" s="1"/>
+      <ns0:c r="D36" s="1" t="n">
+        <ns0:v>357.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E36" s="1" t="n">
+        <ns0:v>340.89</ns0:v>
+      </ns0:c>
       <ns0:c r="F36" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -5894,8 +6034,12 @@
       <ns0:c r="C37" s="1" t="n">
         <ns0:v>9</ns0:v>
       </ns0:c>
-      <ns0:c r="D37" s="1"/>
-      <ns0:c r="E37" s="1"/>
+      <ns0:c r="D37" s="1" t="n">
+        <ns0:v>357.16</ns0:v>
+      </ns0:c>
+      <ns0:c r="E37" s="1" t="n">
+        <ns0:v>345.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F37" s="1" t="n">
         <ns0:v>-50</ns0:v>
       </ns0:c>
@@ -5940,8 +6084,12 @@
       <ns0:c r="C38" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D38" s="1"/>
-      <ns0:c r="E38" s="1"/>
+      <ns0:c r="D38" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E38" s="1" t="n">
+        <ns0:v>351.22</ns0:v>
+      </ns0:c>
       <ns0:c r="F38" s="1" t="n">
         <ns0:v>-80</ns0:v>
       </ns0:c>
@@ -5986,8 +6134,12 @@
       <ns0:c r="C39" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D39" s="1"/>
-      <ns0:c r="E39" s="1"/>
+      <ns0:c r="D39" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E39" s="1" t="n">
+        <ns0:v>359.64</ns0:v>
+      </ns0:c>
       <ns0:c r="F39" s="1" t="n">
         <ns0:v>-80</ns0:v>
       </ns0:c>
@@ -6032,8 +6184,12 @@
       <ns0:c r="C40" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D40" s="1"/>
-      <ns0:c r="E40" s="1"/>
+      <ns0:c r="D40" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E40" s="1" t="n">
+        <ns0:v>359.52</ns0:v>
+      </ns0:c>
       <ns0:c r="F40" s="1" t="n">
         <ns0:v>-80</ns0:v>
       </ns0:c>
@@ -6078,8 +6234,12 @@
       <ns0:c r="C41" s="1" t="n">
         <ns0:v>10</ns0:v>
       </ns0:c>
-      <ns0:c r="D41" s="1"/>
-      <ns0:c r="E41" s="1"/>
+      <ns0:c r="D41" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E41" s="1" t="n">
+        <ns0:v>353.76</ns0:v>
+      </ns0:c>
       <ns0:c r="F41" s="1" t="n">
         <ns0:v>-80</ns0:v>
       </ns0:c>
@@ -6124,8 +6284,12 @@
       <ns0:c r="C42" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D42" s="1"/>
-      <ns0:c r="E42" s="1"/>
+      <ns0:c r="D42" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E42" s="1" t="n">
+        <ns0:v>362.88</ns0:v>
+      </ns0:c>
       <ns0:c r="F42" s="1" t="n">
         <ns0:v>-470</ns0:v>
       </ns0:c>
@@ -6170,8 +6334,12 @@
       <ns0:c r="C43" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D43" s="1"/>
-      <ns0:c r="E43" s="1"/>
+      <ns0:c r="D43" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E43" s="1" t="n">
+        <ns0:v>352.52</ns0:v>
+      </ns0:c>
       <ns0:c r="F43" s="1" t="n">
         <ns0:v>-900</ns0:v>
       </ns0:c>
@@ -6216,8 +6384,12 @@
       <ns0:c r="C44" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D44" s="1"/>
-      <ns0:c r="E44" s="1"/>
+      <ns0:c r="D44" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E44" s="1" t="n">
+        <ns0:v>358.32</ns0:v>
+      </ns0:c>
       <ns0:c r="F44" s="1" t="n">
         <ns0:v>-1303</ns0:v>
       </ns0:c>
@@ -6262,8 +6434,12 @@
       <ns0:c r="C45" s="1" t="n">
         <ns0:v>11</ns0:v>
       </ns0:c>
-      <ns0:c r="D45" s="1"/>
-      <ns0:c r="E45" s="1"/>
+      <ns0:c r="D45" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E45" s="1" t="n">
+        <ns0:v>354.13</ns0:v>
+      </ns0:c>
       <ns0:c r="F45" s="1" t="n">
         <ns0:v>-1358</ns0:v>
       </ns0:c>
@@ -6308,8 +6484,12 @@
       <ns0:c r="C46" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D46" s="1"/>
-      <ns0:c r="E46" s="1"/>
+      <ns0:c r="D46" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E46" s="1" t="n">
+        <ns0:v>338.11</ns0:v>
+      </ns0:c>
       <ns0:c r="F46" s="1" t="n">
         <ns0:v>-1358</ns0:v>
       </ns0:c>
@@ -6354,8 +6534,12 @@
       <ns0:c r="C47" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D47" s="1"/>
-      <ns0:c r="E47" s="1"/>
+      <ns0:c r="D47" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E47" s="1" t="n">
+        <ns0:v>353.76</ns0:v>
+      </ns0:c>
       <ns0:c r="F47" s="1" t="n">
         <ns0:v>-1358</ns0:v>
       </ns0:c>
@@ -6400,8 +6584,12 @@
       <ns0:c r="C48" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D48" s="1"/>
-      <ns0:c r="E48" s="1"/>
+      <ns0:c r="D48" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E48" s="1" t="n">
+        <ns0:v>346.45</ns0:v>
+      </ns0:c>
       <ns0:c r="F48" s="1" t="n">
         <ns0:v>-1358</ns0:v>
       </ns0:c>
@@ -6446,8 +6634,12 @@
       <ns0:c r="C49" s="1" t="n">
         <ns0:v>12</ns0:v>
       </ns0:c>
-      <ns0:c r="D49" s="1"/>
-      <ns0:c r="E49" s="1"/>
+      <ns0:c r="D49" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E49" s="1" t="n">
+        <ns0:v>342.08</ns0:v>
+      </ns0:c>
       <ns0:c r="F49" s="1" t="n">
         <ns0:v>-1358</ns0:v>
       </ns0:c>
@@ -6492,8 +6684,12 @@
       <ns0:c r="C50" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D50" s="1"/>
-      <ns0:c r="E50" s="1"/>
+      <ns0:c r="D50" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E50" s="1" t="n">
+        <ns0:v>344.48</ns0:v>
+      </ns0:c>
       <ns0:c r="F50" s="1" t="n">
         <ns0:v>-1378</ns0:v>
       </ns0:c>
@@ -6538,8 +6734,12 @@
       <ns0:c r="C51" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D51" s="1"/>
-      <ns0:c r="E51" s="1"/>
+      <ns0:c r="D51" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E51" s="1" t="n">
+        <ns0:v>341.17</ns0:v>
+      </ns0:c>
       <ns0:c r="F51" s="1" t="n">
         <ns0:v>-1338</ns0:v>
       </ns0:c>
@@ -6584,8 +6784,12 @@
       <ns0:c r="C52" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D52" s="1"/>
-      <ns0:c r="E52" s="1"/>
+      <ns0:c r="D52" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E52" s="1" t="n">
+        <ns0:v>340</ns0:v>
+      </ns0:c>
       <ns0:c r="F52" s="1" t="n">
         <ns0:v>-1278</ns0:v>
       </ns0:c>
@@ -6630,8 +6834,12 @@
       <ns0:c r="C53" s="1" t="n">
         <ns0:v>13</ns0:v>
       </ns0:c>
-      <ns0:c r="D53" s="1"/>
-      <ns0:c r="E53" s="1"/>
+      <ns0:c r="D53" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E53" s="1" t="n">
+        <ns0:v>256.04</ns0:v>
+      </ns0:c>
       <ns0:c r="F53" s="1" t="n">
         <ns0:v>-1218</ns0:v>
       </ns0:c>
@@ -6676,8 +6884,12 @@
       <ns0:c r="C54" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D54" s="1"/>
-      <ns0:c r="E54" s="1"/>
+      <ns0:c r="D54" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E54" s="1" t="n">
+        <ns0:v>351.41</ns0:v>
+      </ns0:c>
       <ns0:c r="F54" s="1" t="n">
         <ns0:v>-1218</ns0:v>
       </ns0:c>
@@ -6722,8 +6934,12 @@
       <ns0:c r="C55" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D55" s="1"/>
-      <ns0:c r="E55" s="1"/>
+      <ns0:c r="D55" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E55" s="1" t="n">
+        <ns0:v>340.64</ns0:v>
+      </ns0:c>
       <ns0:c r="F55" s="1" t="n">
         <ns0:v>-1218</ns0:v>
       </ns0:c>
@@ -6768,8 +6984,12 @@
       <ns0:c r="C56" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D56" s="1"/>
-      <ns0:c r="E56" s="1"/>
+      <ns0:c r="D56" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E56" s="1" t="n">
+        <ns0:v>352.52</ns0:v>
+      </ns0:c>
       <ns0:c r="F56" s="1" t="n">
         <ns0:v>-1088</ns0:v>
       </ns0:c>
@@ -6814,8 +7034,12 @@
       <ns0:c r="C57" s="1" t="n">
         <ns0:v>14</ns0:v>
       </ns0:c>
-      <ns0:c r="D57" s="1"/>
-      <ns0:c r="E57" s="1"/>
+      <ns0:c r="D57" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E57" s="1" t="n">
+        <ns0:v>344.48</ns0:v>
+      </ns0:c>
       <ns0:c r="F57" s="1" t="n">
         <ns0:v>-923</ns0:v>
       </ns0:c>
@@ -6860,8 +7084,12 @@
       <ns0:c r="C58" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D58" s="1"/>
-      <ns0:c r="E58" s="1"/>
+      <ns0:c r="D58" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E58" s="1" t="n">
+        <ns0:v>344.48</ns0:v>
+      </ns0:c>
       <ns0:c r="F58" s="1" t="n">
         <ns0:v>-703</ns0:v>
       </ns0:c>
@@ -6906,8 +7134,12 @@
       <ns0:c r="C59" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D59" s="1"/>
-      <ns0:c r="E59" s="1"/>
+      <ns0:c r="D59" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E59" s="1" t="n">
+        <ns0:v>340</ns0:v>
+      </ns0:c>
       <ns0:c r="F59" s="1" t="n">
         <ns0:v>-583</ns0:v>
       </ns0:c>
@@ -6952,8 +7184,12 @@
       <ns0:c r="C60" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D60" s="1"/>
-      <ns0:c r="E60" s="1"/>
+      <ns0:c r="D60" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E60" s="1" t="n">
+        <ns0:v>340.89</ns0:v>
+      </ns0:c>
       <ns0:c r="F60" s="1" t="n">
         <ns0:v>-330</ns0:v>
       </ns0:c>
@@ -6998,8 +7234,12 @@
       <ns0:c r="C61" s="1" t="n">
         <ns0:v>15</ns0:v>
       </ns0:c>
-      <ns0:c r="D61" s="1"/>
-      <ns0:c r="E61" s="1"/>
+      <ns0:c r="D61" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
+      <ns0:c r="E61" s="1" t="n">
+        <ns0:v>340.85</ns0:v>
+      </ns0:c>
       <ns0:c r="F61" s="1" t="n">
         <ns0:v>-90</ns0:v>
       </ns0:c>
@@ -7044,8 +7284,12 @@
       <ns0:c r="C62" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D62" s="1"/>
-      <ns0:c r="E62" s="1"/>
+      <ns0:c r="D62" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E62" s="1" t="n">
+        <ns0:v>337.29</ns0:v>
+      </ns0:c>
       <ns0:c r="F62" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7090,8 +7334,12 @@
       <ns0:c r="C63" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D63" s="1"/>
-      <ns0:c r="E63" s="1"/>
+      <ns0:c r="D63" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E63" s="1" t="n">
+        <ns0:v>345.95</ns0:v>
+      </ns0:c>
       <ns0:c r="F63" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7136,8 +7384,12 @@
       <ns0:c r="C64" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D64" s="1"/>
-      <ns0:c r="E64" s="1"/>
+      <ns0:c r="D64" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E64" s="1" t="n">
+        <ns0:v>342.2</ns0:v>
+      </ns0:c>
       <ns0:c r="F64" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7182,8 +7434,12 @@
       <ns0:c r="C65" s="1" t="n">
         <ns0:v>16</ns0:v>
       </ns0:c>
-      <ns0:c r="D65" s="1"/>
-      <ns0:c r="E65" s="1"/>
+      <ns0:c r="D65" s="1" t="n">
+        <ns0:v>344.57</ns0:v>
+      </ns0:c>
+      <ns0:c r="E65" s="1" t="n">
+        <ns0:v>334.39</ns0:v>
+      </ns0:c>
       <ns0:c r="F65" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7228,8 +7484,12 @@
       <ns0:c r="C66" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D66" s="1"/>
-      <ns0:c r="E66" s="1"/>
+      <ns0:c r="D66" s="1" t="n">
+        <ns0:v>371.2</ns0:v>
+      </ns0:c>
+      <ns0:c r="E66" s="1" t="n">
+        <ns0:v>335.61</ns0:v>
+      </ns0:c>
       <ns0:c r="F66" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7274,8 +7534,12 @@
       <ns0:c r="C67" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D67" s="1"/>
-      <ns0:c r="E67" s="1"/>
+      <ns0:c r="D67" s="1" t="n">
+        <ns0:v>371.2</ns0:v>
+      </ns0:c>
+      <ns0:c r="E67" s="1" t="n">
+        <ns0:v>351.6</ns0:v>
+      </ns0:c>
       <ns0:c r="F67" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7320,8 +7584,12 @@
       <ns0:c r="C68" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D68" s="1"/>
-      <ns0:c r="E68" s="1"/>
+      <ns0:c r="D68" s="1" t="n">
+        <ns0:v>371.2</ns0:v>
+      </ns0:c>
+      <ns0:c r="E68" s="1" t="n">
+        <ns0:v>369.57</ns0:v>
+      </ns0:c>
       <ns0:c r="F68" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7366,8 +7634,12 @@
       <ns0:c r="C69" s="1" t="n">
         <ns0:v>17</ns0:v>
       </ns0:c>
-      <ns0:c r="D69" s="1"/>
-      <ns0:c r="E69" s="1"/>
+      <ns0:c r="D69" s="1" t="n">
+        <ns0:v>371.2</ns0:v>
+      </ns0:c>
+      <ns0:c r="E69" s="1" t="n">
+        <ns0:v>377.64</ns0:v>
+      </ns0:c>
       <ns0:c r="F69" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7412,8 +7684,12 @@
       <ns0:c r="C70" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D70" s="1"/>
-      <ns0:c r="E70" s="1"/>
+      <ns0:c r="D70" s="1" t="n">
+        <ns0:v>441.55</ns0:v>
+      </ns0:c>
+      <ns0:c r="E70" s="1" t="n">
+        <ns0:v>382.35</ns0:v>
+      </ns0:c>
       <ns0:c r="F70" s="1" t="n">
         <ns0:v>130</ns0:v>
       </ns0:c>
@@ -7458,8 +7734,12 @@
       <ns0:c r="C71" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D71" s="1"/>
-      <ns0:c r="E71" s="1"/>
+      <ns0:c r="D71" s="1" t="n">
+        <ns0:v>441.55</ns0:v>
+      </ns0:c>
+      <ns0:c r="E71" s="1" t="n">
+        <ns0:v>390.83</ns0:v>
+      </ns0:c>
       <ns0:c r="F71" s="1" t="n">
         <ns0:v>160</ns0:v>
       </ns0:c>
@@ -7504,8 +7784,12 @@
       <ns0:c r="C72" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D72" s="1"/>
-      <ns0:c r="E72" s="1"/>
+      <ns0:c r="D72" s="1" t="n">
+        <ns0:v>441.55</ns0:v>
+      </ns0:c>
+      <ns0:c r="E72" s="1" t="n">
+        <ns0:v>395.7</ns0:v>
+      </ns0:c>
       <ns0:c r="F72" s="1" t="n">
         <ns0:v>190</ns0:v>
       </ns0:c>
@@ -7550,8 +7834,12 @@
       <ns0:c r="C73" s="1" t="n">
         <ns0:v>18</ns0:v>
       </ns0:c>
-      <ns0:c r="D73" s="1"/>
-      <ns0:c r="E73" s="1"/>
+      <ns0:c r="D73" s="1" t="n">
+        <ns0:v>441.55</ns0:v>
+      </ns0:c>
+      <ns0:c r="E73" s="1" t="n">
+        <ns0:v>392.79</ns0:v>
+      </ns0:c>
       <ns0:c r="F73" s="1" t="n">
         <ns0:v>190</ns0:v>
       </ns0:c>
@@ -7596,8 +7884,12 @@
       <ns0:c r="C74" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D74" s="1"/>
-      <ns0:c r="E74" s="1"/>
+      <ns0:c r="D74" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E74" s="1" t="n">
+        <ns0:v>387.98</ns0:v>
+      </ns0:c>
       <ns0:c r="F74" s="1" t="n">
         <ns0:v>90</ns0:v>
       </ns0:c>
@@ -7642,8 +7934,12 @@
       <ns0:c r="C75" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D75" s="1"/>
-      <ns0:c r="E75" s="1"/>
+      <ns0:c r="D75" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E75" s="1" t="n">
+        <ns0:v>386.85</ns0:v>
+      </ns0:c>
       <ns0:c r="F75" s="1" t="n">
         <ns0:v>90</ns0:v>
       </ns0:c>
@@ -7688,8 +7984,12 @@
       <ns0:c r="C76" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D76" s="1"/>
-      <ns0:c r="E76" s="1"/>
+      <ns0:c r="D76" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E76" s="1" t="n">
+        <ns0:v>391.25</ns0:v>
+      </ns0:c>
       <ns0:c r="F76" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -7734,8 +8034,12 @@
       <ns0:c r="C77" s="1" t="n">
         <ns0:v>19</ns0:v>
       </ns0:c>
-      <ns0:c r="D77" s="1"/>
-      <ns0:c r="E77" s="1"/>
+      <ns0:c r="D77" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E77" s="1" t="n">
+        <ns0:v>383.89</ns0:v>
+      </ns0:c>
       <ns0:c r="F77" s="1" t="n">
         <ns0:v>30</ns0:v>
       </ns0:c>
@@ -7780,8 +8084,12 @@
       <ns0:c r="C78" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D78" s="1"/>
-      <ns0:c r="E78" s="1"/>
+      <ns0:c r="D78" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E78" s="1" t="n">
+        <ns0:v>373.95</ns0:v>
+      </ns0:c>
       <ns0:c r="F78" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7826,8 +8134,12 @@
       <ns0:c r="C79" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D79" s="1"/>
-      <ns0:c r="E79" s="1"/>
+      <ns0:c r="D79" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E79" s="1" t="n">
+        <ns0:v>368.17</ns0:v>
+      </ns0:c>
       <ns0:c r="F79" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7872,8 +8184,12 @@
       <ns0:c r="C80" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D80" s="1"/>
-      <ns0:c r="E80" s="1"/>
+      <ns0:c r="D80" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E80" s="1" t="n">
+        <ns0:v>367.1</ns0:v>
+      </ns0:c>
       <ns0:c r="F80" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7918,8 +8234,12 @@
       <ns0:c r="C81" s="1" t="n">
         <ns0:v>20</ns0:v>
       </ns0:c>
-      <ns0:c r="D81" s="1"/>
-      <ns0:c r="E81" s="1"/>
+      <ns0:c r="D81" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E81" s="1" t="n">
+        <ns0:v>357.61</ns0:v>
+      </ns0:c>
       <ns0:c r="F81" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -7964,8 +8284,12 @@
       <ns0:c r="C82" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D82" s="1"/>
-      <ns0:c r="E82" s="1"/>
+      <ns0:c r="D82" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E82" s="1" t="n">
+        <ns0:v>357.16</ns0:v>
+      </ns0:c>
       <ns0:c r="F82" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8010,8 +8334,12 @@
       <ns0:c r="C83" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D83" s="1"/>
-      <ns0:c r="E83" s="1"/>
+      <ns0:c r="D83" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E83" s="1" t="n">
+        <ns0:v>359.07</ns0:v>
+      </ns0:c>
       <ns0:c r="F83" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8056,8 +8384,12 @@
       <ns0:c r="C84" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D84" s="1"/>
-      <ns0:c r="E84" s="1"/>
+      <ns0:c r="D84" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E84" s="1" t="n">
+        <ns0:v>352.04</ns0:v>
+      </ns0:c>
       <ns0:c r="F84" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8102,8 +8434,12 @@
       <ns0:c r="C85" s="1" t="n">
         <ns0:v>21</ns0:v>
       </ns0:c>
-      <ns0:c r="D85" s="1"/>
-      <ns0:c r="E85" s="1"/>
+      <ns0:c r="D85" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E85" s="1" t="n">
+        <ns0:v>358.01</ns0:v>
+      </ns0:c>
       <ns0:c r="F85" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8148,8 +8484,12 @@
       <ns0:c r="C86" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D86" s="1"/>
-      <ns0:c r="E86" s="1"/>
+      <ns0:c r="D86" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E86" s="1" t="n">
+        <ns0:v>364</ns0:v>
+      </ns0:c>
       <ns0:c r="F86" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8194,8 +8534,12 @@
       <ns0:c r="C87" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D87" s="1"/>
-      <ns0:c r="E87" s="1"/>
+      <ns0:c r="D87" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E87" s="1" t="n">
+        <ns0:v>366.92</ns0:v>
+      </ns0:c>
       <ns0:c r="F87" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8240,8 +8584,12 @@
       <ns0:c r="C88" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D88" s="1"/>
-      <ns0:c r="E88" s="1"/>
+      <ns0:c r="D88" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E88" s="1" t="n">
+        <ns0:v>371.23</ns0:v>
+      </ns0:c>
       <ns0:c r="F88" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8286,8 +8634,12 @@
       <ns0:c r="C89" s="1" t="n">
         <ns0:v>22</ns0:v>
       </ns0:c>
-      <ns0:c r="D89" s="1"/>
-      <ns0:c r="E89" s="1"/>
+      <ns0:c r="D89" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E89" s="1" t="n">
+        <ns0:v>372.51</ns0:v>
+      </ns0:c>
       <ns0:c r="F89" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8332,8 +8684,12 @@
       <ns0:c r="C90" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D90" s="1"/>
-      <ns0:c r="E90" s="1"/>
+      <ns0:c r="D90" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E90" s="1" t="n">
+        <ns0:v>376.22</ns0:v>
+      </ns0:c>
       <ns0:c r="F90" s="1" t="n">
         <ns0:v>30</ns0:v>
       </ns0:c>
@@ -8378,8 +8734,12 @@
       <ns0:c r="C91" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D91" s="1"/>
-      <ns0:c r="E91" s="1"/>
+      <ns0:c r="D91" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E91" s="1" t="n">
+        <ns0:v>380.76</ns0:v>
+      </ns0:c>
       <ns0:c r="F91" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -8424,8 +8784,12 @@
       <ns0:c r="C92" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D92" s="1"/>
-      <ns0:c r="E92" s="1"/>
+      <ns0:c r="D92" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E92" s="1" t="n">
+        <ns0:v>376.36</ns0:v>
+      </ns0:c>
       <ns0:c r="F92" s="1" t="n">
         <ns0:v>60</ns0:v>
       </ns0:c>
@@ -8470,8 +8834,12 @@
       <ns0:c r="C93" s="1" t="n">
         <ns0:v>23</ns0:v>
       </ns0:c>
-      <ns0:c r="D93" s="1"/>
-      <ns0:c r="E93" s="1"/>
+      <ns0:c r="D93" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E93" s="1" t="n">
+        <ns0:v>380.86</ns0:v>
+      </ns0:c>
       <ns0:c r="F93" s="1" t="n">
         <ns0:v>30</ns0:v>
       </ns0:c>
@@ -8516,8 +8884,12 @@
       <ns0:c r="C94" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D94" s="1"/>
-      <ns0:c r="E94" s="1"/>
+      <ns0:c r="D94" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E94" s="1" t="n">
+        <ns0:v>382.42</ns0:v>
+      </ns0:c>
       <ns0:c r="F94" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8562,8 +8934,12 @@
       <ns0:c r="C95" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D95" s="1"/>
-      <ns0:c r="E95" s="1"/>
+      <ns0:c r="D95" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E95" s="1" t="n">
+        <ns0:v>380.14</ns0:v>
+      </ns0:c>
       <ns0:c r="F95" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8608,8 +8984,12 @@
       <ns0:c r="C96" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D96" s="1"/>
-      <ns0:c r="E96" s="1"/>
+      <ns0:c r="D96" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E96" s="1" t="n">
+        <ns0:v>370.69</ns0:v>
+      </ns0:c>
       <ns0:c r="F96" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
@@ -8656,8 +9036,12 @@
       <ns0:c r="C97" s="1" t="n">
         <ns0:v>24</ns0:v>
       </ns0:c>
-      <ns0:c r="D97" s="1"/>
-      <ns0:c r="E97" s="1"/>
+      <ns0:c r="D97" s="1" t="n">
+        <ns0:v>371.42</ns0:v>
+      </ns0:c>
+      <ns0:c r="E97" s="1" t="n">
+        <ns0:v>366.92</ns0:v>
+      </ns0:c>
       <ns0:c r="F97" s="1" t="n">
         <ns0:v>0</ns0:v>
       </ns0:c>
